--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Pukal Rokka</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9861050515</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9861050515</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -944,10 +942,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -958,7 +954,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1007,7 +1003,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1298,7 +1294,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -517,8 +517,8 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -980,6 +980,205 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 8:30 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364527</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9841732382</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9801970444</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Tikhedewal Chumlung Kirati Bhawan, , ,</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>bkeeshahi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 1m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -994,11 +1193,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1031,7 +1230,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1052,7 +1251,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1113,216 +1312,257 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1366504</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Pukal Rokka</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : no light in router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 12:58:44 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>18h 32m</t>
         </is>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1050,10 +1050,8 @@
           <t>Vicky Shahi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9841732382</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9841732382</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1139,10 +1137,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1153,7 +1149,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1173,6 +1173,217 @@
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 8:48 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:48:55 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:48:55 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.70175</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>27.655793801439316, 85.34194749764016, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>regmiashutosh3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>03:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB091A</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.3341</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>6d 13h 50m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1189,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1198,7 +1409,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1226,7 +1437,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1447,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1247,7 +1458,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1482,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 32m</t>
+          <t>3d 16h 11m</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1523,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1599,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1561,6 +1772,73 @@
       <c r="M20" s="3" t="inlineStr">
         <is>
           <t>18h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:48:55 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:48:55 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1245,10 +1245,8 @@
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9867171444</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9867171444</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1283,10 +1281,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.70175</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.70175</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1342,25 +1338,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB091A</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.3341</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33410000000001</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1409,7 +1401,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1808,7 +1800,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -512,24 +512,24 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1378,6 +1378,627 @@
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:28 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>no light issue in stb box</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364855</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9808426033</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 08:46:00 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808426033</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:05 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:28:48 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>OM Shanti Chock - Palace Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>hellosachhami0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>2d 12h 42m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 40m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:26 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366738</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:26:16 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.69367</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>"Near to Ananda Events &amp; Meetings Pvt.Ltd.,Shantinagar New Baneshwor Kathmandu Bagmati, Kathmandu 44</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>suman.puri2057@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L27-5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.34479</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:18 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>upgrade to router</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366896</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Jonik Jung Thapa</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Jonik Jung Thapa</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9868731490</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9840418268</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:54:00 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.68117</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Mahadevsthan bridge, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>jishanjungthapa12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Bajgain</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.33836</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>15h 24m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1392,16 +2013,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1429,7 +2050,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1439,7 +2060,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1450,7 +2071,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +2095,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 16h 11m</t>
+          <t>2d 15h 55m</t>
         </is>
       </c>
     </row>
@@ -1515,10 +2136,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1533,14 +2154,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1591,10 +2212,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1610,227 +2231,317 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1366504</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Pukal Rokka</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 12:58:44 PM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>TKT1366504</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Pukal Rokka</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:31:06 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:58:44 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:31:06 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>TKT1359809</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 06:58:32 PM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>6d 13h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366896</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Jonik Jung Thapa</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:54:00 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>15h 24m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1448,10 +1448,8 @@
           <t>Sachit Achhami</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9808426033</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9808426033</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1523,10 +1521,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="inlineStr"/>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1541,10 +1537,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1555,7 +1549,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1651,10 +1645,8 @@
           <t>Suman Puri</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9860372268</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9860372268</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1689,10 +1681,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.69367</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.69367</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1744,25 +1734,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L27-5</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.34479</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.34479</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1848,20 +1834,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Jonik Jung Thapa</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9868731490</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9868731490</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1896,10 +1876,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.68117</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.68117</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1955,25 +1933,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.33836</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.33835999999999</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2022,7 +1996,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2511,7 +2485,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1971,6 +1971,217 @@
         </is>
       </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:56 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366738</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.69367</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>"Near to Ananda Events &amp; Meetings Pvt.Ltd.,Shantinagar New Baneshwor Kathmandu Bagmati, Kathmandu 44</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>suman.puri2057@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L27-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.34479</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>17h 51m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1987,7 +2198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1996,7 +2207,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2024,7 +2235,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2034,7 +2245,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2045,7 +2256,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2280,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 15h 55m</t>
+          <t>2d 4h 24m</t>
         </is>
       </c>
     </row>
@@ -2110,14 +2321,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2186,14 +2397,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2516,6 +2727,73 @@
       <c r="M23" s="5" t="inlineStr">
         <is>
           <t>15h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366738</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>17h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -2043,10 +2043,8 @@
           <t>Suman Puri</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860372268</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860372268</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2081,10 +2079,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.69367</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.69367</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2140,48 +2136,247 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L27-5</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.34479</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.34479</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>17h 51m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Router / Adapter Faulty</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366999</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Surya moktan</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Surya moktan</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9803523762</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9803523762</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:08:23 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>00:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>17h 51m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 7m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -2198,13 +2393,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -2235,7 +2430,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2245,7 +2440,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2256,7 +2451,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2475,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 4h 24m</t>
+          <t>1d 20h 57m</t>
         </is>
       </c>
     </row>
@@ -2339,14 +2534,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2634,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -2454,167 +2649,123 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1366504</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Pukal Rokka</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 12:58:44 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1359809</t>
+          <t>TKT1366504</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Ashutosh Regmi</t>
+          <t>Pukal Rokka</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2634,22 +2785,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 06:58:32 PM</t>
+          <t>11 Oct 2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2659,19 +2810,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>6d 13h 50m</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1366896</t>
+          <t>TKT1359809</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Jonik Jung Thapa</t>
+          <t>Ashutosh Regmi</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2701,22 +2852,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:54:00 PM</t>
+          <t>05 Oct 2026 06:58:32 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2726,74 +2877,208 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>15h 24m</t>
+          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>TKT1366896</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Jonik Jung Thapa</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:54:00 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>15h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1366738</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Suman Puri</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 04:04:04 PM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>17h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366999</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Surya moktan</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:08:23 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>15h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -2246,10 +2246,8 @@
           <t>Surya moktan</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9803523762</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9803523762</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2317,10 +2315,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2339,10 +2335,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2353,32 +2347,243 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 7m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366755</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Godhuli Enterprise</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Godhuli Enterprise</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9851064611</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25:26 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9801822380</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:23:45 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25:26 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.68092</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor, Mahadevsthan, suryadarshan tole, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>godhulienter@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>00:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.33994</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>15h 7m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2430,7 +2635,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2440,7 +2645,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2451,7 +2656,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2680,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 57m</t>
+          <t>1d 16h 27m</t>
         </is>
       </c>
     </row>
@@ -2516,14 +2721,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2592,14 +2797,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3048,14 +3253,14 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
           <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 10:15:42 AM</t>
@@ -3079,6 +3284,73 @@
       <c r="M26" s="3" t="inlineStr">
         <is>
           <t>15h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366755</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Godhuli Enterprise</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25:26 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:23:45 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25:26 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2443,10 +2443,8 @@
           <t>Godhuli Enterprise</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9851064611</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9851064611</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2481,10 +2479,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.68092</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.68092</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2540,50 +2536,249 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.33994</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.33994</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366652</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>karma gurung</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>karma gurung</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841238889</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20:22 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841238889</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:46:35 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20:22 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Buddha , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>abcde@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>00:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L47-8</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>18h 1m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW10" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2635,7 +2830,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2645,7 +2840,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2656,7 +2851,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2875,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 27m</t>
+          <t>1d 13h 28m</t>
         </is>
       </c>
     </row>
@@ -2750,84 +2945,79 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2839,18 +3029,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2862,7 +3052,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2877,234 +3067,146 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1366504</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Pukal Rokka</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 12:58:44 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1359809</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Ashutosh Regmi</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 06:58:32 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1366896</t>
+          <t>TKT1366504</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Jonik Jung Thapa</t>
+          <t>Pukal Rokka</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -3124,22 +3226,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:54:00 PM</t>
+          <t>11 Oct 2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3149,19 +3251,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>15h 24m</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1366738</t>
+          <t>TKT1359809</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Suman Puri</t>
+          <t>Ashutosh Regmi</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3191,22 +3293,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:04:04 PM</t>
+          <t>05 Oct 2026 06:58:32 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -3216,29 +3318,29 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>17h 51m</t>
+          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1366999</t>
+          <t>TKT1366896</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Surya moktan</t>
+          <t>Jonik Jung Thapa</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3258,22 +3360,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:08:23 PM</t>
+          <t>11 Oct 2026 05:54:00 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3283,74 +3385,275 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>15h 7m</t>
+          <t>15h 24m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>TKT1366738</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>17h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366999</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Surya moktan</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:08:23 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>15h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>TKT1366755</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Godhuli Enterprise</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 04:23:45 PM</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>18h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366652</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>karma gurung</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20:22 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:46:35 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20:22 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2646,10 +2646,8 @@
           <t>karma gurung</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841238889</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841238889</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2739,10 +2737,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -2753,32 +2749,454 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366558</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9860272522</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59:25 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9860272522</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:34:59 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59:25 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.6735</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Kumaripati Purnachandi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>rabindra_shr@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L43A-1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.31907</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>19h 33m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 24m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367161</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9802084488</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9802084488</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:53:31 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73021</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>IOM International Organization for Migration Nepal - Non-profit organization Kathmandu 44600, Bagmat</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>yog354s@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>01:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L62-2</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.331738</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2793,7 +3211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2830,7 +3248,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2840,7 +3258,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2851,7 +3269,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2875,7 +3293,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 28m</t>
+          <t>1d 9h 6m</t>
         </is>
       </c>
     </row>
@@ -2916,14 +3334,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3010,14 +3428,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3623,14 +4041,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 10:20:22 AM</t>
@@ -3654,6 +4072,140 @@
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t>19h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366558</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Rabindra Shrestha</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59:25 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:34:59 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59:25 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>21h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367161</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:53:31 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -2845,10 +2845,8 @@
           <t>Rabindra Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9860272522</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9860272522</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2883,10 +2881,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.6735</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.6735</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2942,25 +2938,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L43A-1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.31907</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.31907</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3056,10 +3048,8 @@
           <t>Yogesh Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9802084488</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9802084488</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3094,10 +3084,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73021</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73021</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3153,48 +3141,454 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L62-2</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.331738</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.331738</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>setup box issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366814</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9865121028</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9865121028</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:12:53 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.655215</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Gamcha chowk near, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>01:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Abina Chitrakar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L46-2</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.393444</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>14h 7m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>17h 56m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6 upgardation</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366937</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Anita Bogati</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Anita Bogati</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9860370065</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10:48 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860673598</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:35:19 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10:48 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dallu Awasiya Vidhyalaya - Educational institution P852+V23 15 ??????? ????? Kathmandu 44600, Kathma</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>ms.anitabogati@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>01:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>16h 35m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3211,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3248,7 +3642,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3258,7 +3652,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3269,7 +3663,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3687,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 9h 6m</t>
+          <t>1d 6h 13m</t>
         </is>
       </c>
     </row>
@@ -3334,14 +3728,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -3352,14 +3746,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3428,14 +3822,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -3451,14 +3845,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4502,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -4175,14 +4569,14 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 11:01:30 AM</t>
@@ -4206,6 +4600,140 @@
       <c r="M32" s="3" t="inlineStr">
         <is>
           <t>14h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366814</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:12:53 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>17h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366937</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Anita Bogati</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10:48 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:35:19 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10:48 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>16h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3251,10 +3251,8 @@
           <t>Pabitra khatri</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9865121028</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9865121028</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3289,10 +3287,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.655215</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.655215</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3344,25 +3340,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L46-2</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.393444</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.393444</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3458,10 +3450,8 @@
           <t>Anita Bogati</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9860370065</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9860370065</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3541,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3565,32 +3553,135 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>16h 35m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>16h 35m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3614,7 +3705,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3642,7 +3733,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3663,7 +3754,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -3775,84 +3866,75 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>77.8%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -3864,18 +3946,18 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3969,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -3905,12 +3987,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3925,234 +4007,138 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1366504</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Pukal Rokka</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 12:58:44 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1359809</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Ashutosh Regmi</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 06:58:32 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>6d 13h 50m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1366896</t>
+          <t>TKT1366504</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Jonik Jung Thapa</t>
+          <t>Pukal Rokka</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -4172,22 +4158,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:54:00 PM</t>
+          <t>11 Oct 2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4197,19 +4183,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>15h 24m</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1366738</t>
+          <t>TKT1359809</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Suman Puri</t>
+          <t>Ashutosh Regmi</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4239,22 +4225,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:04:04 PM</t>
+          <t>05 Oct 2026 06:58:32 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4264,29 +4250,29 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>17h 51m</t>
+          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1366999</t>
+          <t>TKT1366896</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Surya moktan</t>
+          <t>Jonik Jung Thapa</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4306,22 +4292,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:08:23 PM</t>
+          <t>11 Oct 2026 05:54:00 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4331,19 +4317,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>15h 7m</t>
+          <t>15h 24m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1366755</t>
+          <t>TKT1366738</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Godhuli Enterprise</t>
+          <t>Suman Puri</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4373,22 +4359,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:25:26 AM</t>
+          <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:23:45 PM</t>
+          <t>11 Oct 2026 04:04:04 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:25:26 AM</t>
+          <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -4398,29 +4384,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>17h 51m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1366652</t>
+          <t>TKT1366999</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>karma gurung</t>
+          <t>Surya moktan</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4440,22 +4426,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:20:22 AM</t>
+          <t>12 Oct 2026 10:15:42 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:46:35 PM</t>
+          <t>11 Oct 2026 07:08:23 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:20:22 AM</t>
+          <t>12 Oct 2026 10:15:42 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4465,19 +4451,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>15h 7m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1366558</t>
+          <t>TKT1366755</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Rabindra Shrestha</t>
+          <t>Godhuli Enterprise</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4507,22 +4493,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:59:25 AM</t>
+          <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:34:59 PM</t>
+          <t>11 Oct 2026 04:23:45 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:59:25 AM</t>
+          <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4532,29 +4518,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>21h 24m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1367161</t>
+          <t>TKT1366652</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Yogesh Shrestha</t>
+          <t>karma gurung</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4574,22 +4560,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:01:30 AM</t>
+          <t>12 Oct 2026 10:20:22 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:53:31 PM</t>
+          <t>11 Oct 2026 02:46:35 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:01:30 AM</t>
+          <t>12 Oct 2026 10:20:22 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4599,29 +4585,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1366814</t>
+          <t>TKT1366558</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Pabitra khatri</t>
+          <t>Rabindra Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4636,27 +4622,27 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:09:44 AM</t>
+          <t>12 Oct 2026 10:59:25 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:12:53 PM</t>
+          <t>11 Oct 2026 01:34:59 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:09:44 AM</t>
+          <t>12 Oct 2026 10:59:25 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -4666,72 +4652,206 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>17h 56m</t>
+          <t>21h 24m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>TKT1367161</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:53:31 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366814</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:12:53 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>17h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>TKT1366937</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Anita Bogati</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 11:10:48 AM</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 06:35:19 PM</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 11:10:48 AM</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>16h 35m</t>
         </is>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3685,6 +3685,611 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367285</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Menuka adhikari</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Menuka adhikari</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9829343940</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28:58 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9829343940</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:47:07 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28:58 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Chamati, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>01:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>3h 41m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367040</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9860985865</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:44:48 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860985865</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:30:34 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:46:45 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Radha Krishna Temple, Raniban - Hindu temple P7JP+2X5 Radha Krishna Chowk, Yerahity Raniban Rd Nagar</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9860985865@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB647</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>14h 1m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>16h 16m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364527</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841732382</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9801970444</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Tikhedewal Chumlung Kirati Bhawan, , ,</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>bkeeshahi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>18:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 9m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3696,7 +4301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3705,7 +4310,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3733,7 +4338,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -3743,7 +4348,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3754,7 +4359,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -3778,7 +4383,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 13m</t>
+          <t>1d 7h 15m</t>
         </is>
       </c>
     </row>
@@ -3819,14 +4424,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -3837,14 +4442,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -3855,14 +4460,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3927,14 +4532,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -3973,10 +4578,10 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -4019,14 +4624,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4857,6 +5462,140 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367285</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Menuka adhikari</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28:58 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:47:07 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28:58 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>3h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364527</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 9m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3752,10 +3752,8 @@
           <t>Menuka adhikari</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9829343940</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9829343940</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3841,10 +3839,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3855,7 +3851,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3951,10 +3947,8 @@
           <t>Deepak Babu Bhatta</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9860985865</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9860985865</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4026,10 +4020,8 @@
           <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH18" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="inlineStr"/>
       <c r="AJ18" s="3" t="inlineStr"/>
@@ -4044,10 +4036,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4058,7 +4048,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4154,10 +4144,8 @@
           <t>Vicky Shahi</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841732382</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841732382</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4247,10 +4235,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4261,32 +4247,446 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 9m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:56 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367391</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Priyasha Shah</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Priyasha Shah</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861494544</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:09:03 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9861494544</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:09:03 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:56:37 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.67509</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Bhatbhateni - Opposite By Cosmic International Academy, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>priyashashah37@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.34637</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>no light issue in stb box</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364855</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9808426033</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51:04 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808426033</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:05 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51:04 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>OM Shanti Chock - Palace Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>hellosachhami0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>14:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 9m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4338,7 +4738,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4348,7 +4748,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4359,7 +4759,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4783,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7h 15m</t>
+          <t>1d 9h 44m</t>
         </is>
       </c>
     </row>
@@ -4424,14 +4824,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -4442,14 +4842,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -4532,14 +4932,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -4555,14 +4955,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5895,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -5562,14 +5962,14 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>12 Oct 2026 11:38:26 AM</t>
@@ -5593,6 +5993,73 @@
       <c r="M38" s="3" t="inlineStr">
         <is>
           <t>2d 22h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364855</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51:04 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:05 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51:04 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>2d 18h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -4343,10 +4343,8 @@
           <t>Priyasha Shah</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861494544</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861494544</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4381,10 +4379,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.67509</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.67509</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4436,25 +4432,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.34637</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.34636999999999</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4550,10 +4542,8 @@
           <t>Sachit Achhami</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9808426033</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9808426033</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4625,10 +4615,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH21" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH21" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
@@ -4647,10 +4635,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4661,32 +4647,454 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366549</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9860577686</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10:17 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841728074</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:28:33 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10:17 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.73023</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Tushal Multivenue - Event venue Tushal 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>adhikarihrithik2022@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L55-4</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.3151</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>2d 18h 2m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>22h 41m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367312</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Tilak bahadur bohora</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Tilak bahadur bohora</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841279916</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841279916</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:28:49 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.735677</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Sweet Heart Montessori &amp; Day Care Bohoratar road, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>anjilabohora76@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>02:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.295385</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3h 35m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4701,7 +5109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4738,7 +5146,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4748,7 +5156,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4759,7 +5167,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -4783,7 +5191,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 9h 44m</t>
+          <t>1d 7h 9m</t>
         </is>
       </c>
     </row>
@@ -4824,14 +5232,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -4932,14 +5340,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -6029,14 +6437,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 11:51:04 AM</t>
@@ -6060,6 +6468,140 @@
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>2d 18h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366549</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10:17 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:28:33 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10:17 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>22h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367312</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Tilak bahadur bohora</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:28:49 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>3h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4743,10 +4743,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9860577686</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9860577686</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4779,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.73023</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.73023</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4840,25 +4836,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L55-4</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.3151</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.3151</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4954,10 +4946,8 @@
           <t>Tilak bahadur bohora</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841279916</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841279916</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4992,10 +4982,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.735677</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.735677</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5051,25 +5039,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.295385</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.295385</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5118,7 +5102,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6504,7 +6488,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6571,7 +6555,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5082,6 +5082,217 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367602</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Roji Shrestha</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Roji Shrestha</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9840050285</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41:01 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9840050285</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:53:33 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41:01 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67496</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>near Panga Dobato Bus Stop Panga Rd, Kirtipur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>ara.readymade@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>01:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB141</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.28072</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5093,7 +5304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5102,7 +5313,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5130,7 +5341,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -5140,7 +5351,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -5151,7 +5362,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5386,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7h 9m</t>
+          <t>1d 5h 26m</t>
         </is>
       </c>
     </row>
@@ -5216,14 +5427,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -5324,14 +5535,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -6589,6 +6800,73 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367602</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Roji Shrestha</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41:01 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:53:33 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41:01 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW24"/>
+  <dimension ref="A1:AW29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -5149,10 +5149,8 @@
           <t>Roji Shrestha</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9840050285</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9840050285</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5187,10 +5185,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67496</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67496</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5246,48 +5242,1051 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB141</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.28072</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.28072</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>1h 47m</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>stb adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366894</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9848949572</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:10:46 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848949572</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:52:33 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57:32 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Khadka Gaun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9811155449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>02:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>18h 46m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>19h 4m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:56 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>stb adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366894</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9848949572</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:10:46 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848949572</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:52:33 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57:32 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Khadka Gaun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>9811155449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>02:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>18h 46m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>19h 4m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:54 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366465</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Adhikari</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Adhikari</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9840779767</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:38:47 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>KLK9840779767</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:38:47 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:54:48 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>27.696517, 85.289584 - Makalu Oil Store, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>sunitarijal45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB318</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>27.690688, 85.250552, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>09:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB594</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>27.690688, 85.250552, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>09:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB594</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5304,13 +6303,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -5341,7 +6340,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -5351,7 +6350,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -5362,7 +6361,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -5374,7 +6373,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>7h 9m</t>
         </is>
       </c>
     </row>
@@ -5386,7 +6385,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 26m</t>
+          <t>1d 5h 56m</t>
         </is>
       </c>
     </row>
@@ -5427,14 +6426,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -5445,14 +6444,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -5535,14 +6534,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -5554,18 +6553,18 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5577,18 +6576,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5600,14 +6599,14 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5618,202 +6617,158 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1366504</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Pukal Rokka</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 12:58:44 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1359809</t>
+          <t>TKT1366504</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Ashutosh Regmi</t>
+          <t>Pukal Rokka</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -5833,22 +6788,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 06:58:32 PM</t>
+          <t>11 Oct 2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5858,19 +6813,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>6d 13h 50m</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1366896</t>
+          <t>TKT1359809</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Jonik Jung Thapa</t>
+          <t>Ashutosh Regmi</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5900,22 +6855,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:54:00 PM</t>
+          <t>05 Oct 2026 06:58:32 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -5925,19 +6880,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>15h 24m</t>
+          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1366738</t>
+          <t>TKT1366896</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Suman Puri</t>
+          <t>Jonik Jung Thapa</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5967,22 +6922,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:04:04 PM</t>
+          <t>11 Oct 2026 05:54:00 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5992,29 +6947,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>17h 51m</t>
+          <t>15h 24m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1366999</t>
+          <t>TKT1366738</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Surya moktan</t>
+          <t>Suman Puri</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -6034,22 +6989,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:08:23 PM</t>
+          <t>11 Oct 2026 04:04:04 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -6059,29 +7014,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>15h 7m</t>
+          <t>17h 51m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1366755</t>
+          <t>TKT1366999</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Godhuli Enterprise</t>
+          <t>Surya moktan</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -6101,22 +7056,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:25:26 AM</t>
+          <t>12 Oct 2026 10:15:42 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:23:45 PM</t>
+          <t>11 Oct 2026 07:08:23 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:25:26 AM</t>
+          <t>12 Oct 2026 10:15:42 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -6126,29 +7081,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>15h 7m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1366652</t>
+          <t>TKT1366755</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>karma gurung</t>
+          <t>Godhuli Enterprise</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -6168,22 +7123,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:20:22 AM</t>
+          <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:46:35 PM</t>
+          <t>11 Oct 2026 04:23:45 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:20:22 AM</t>
+          <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -6193,29 +7148,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1366558</t>
+          <t>TKT1366652</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Rabindra Shrestha</t>
+          <t>karma gurung</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6235,22 +7190,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:59:25 AM</t>
+          <t>12 Oct 2026 10:20:22 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:34:59 PM</t>
+          <t>11 Oct 2026 02:46:35 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:59:25 AM</t>
+          <t>12 Oct 2026 10:20:22 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -6260,19 +7215,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>21h 24m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1367161</t>
+          <t>TKT1366558</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Yogesh Shrestha</t>
+          <t>Rabindra Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6302,22 +7257,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:01:30 AM</t>
+          <t>12 Oct 2026 10:59:25 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:53:31 PM</t>
+          <t>11 Oct 2026 01:34:59 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:01:30 AM</t>
+          <t>12 Oct 2026 10:59:25 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -6327,29 +7282,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>21h 24m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1366814</t>
+          <t>TKT1367161</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Pabitra khatri</t>
+          <t>Yogesh Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -6369,22 +7324,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:09:44 AM</t>
+          <t>12 Oct 2026 11:01:30 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:12:53 PM</t>
+          <t>11 Oct 2026 08:53:31 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:09:44 AM</t>
+          <t>12 Oct 2026 11:01:30 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -6394,29 +7349,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>17h 56m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1366937</t>
+          <t>TKT1366814</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Anita Bogati</t>
+          <t>Pabitra khatri</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6436,22 +7391,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:10:48 AM</t>
+          <t>12 Oct 2026 11:09:44 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 06:35:19 PM</t>
+          <t>11 Oct 2026 05:12:53 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:10:48 AM</t>
+          <t>12 Oct 2026 11:09:44 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6461,29 +7416,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>16h 35m</t>
+          <t>17h 56m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1367285</t>
+          <t>TKT1366937</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Menuka adhikari</t>
+          <t>Anita Bogati</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6503,22 +7458,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:28:58 AM</t>
+          <t>12 Oct 2026 11:10:48 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 07:47:07 AM</t>
+          <t>11 Oct 2026 06:35:19 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:28:58 AM</t>
+          <t>12 Oct 2026 11:10:48 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -6528,29 +7483,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>3h 41m</t>
+          <t>16h 35m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1364527</t>
+          <t>TKT1367285</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Vicky Shahi</t>
+          <t>Menuka adhikari</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6570,22 +7525,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:38:26 AM</t>
+          <t>12 Oct 2026 11:28:58 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:28:36 PM</t>
+          <t>12 Oct 2026 07:47:07 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:38:26 AM</t>
+          <t>12 Oct 2026 11:28:58 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -6595,29 +7550,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 22h 9m</t>
+          <t>3h 41m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364855</t>
+          <t>TKT1364527</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sachit Achhami</t>
+          <t>Vicky Shahi</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -6637,22 +7592,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:51:04 AM</t>
+          <t>12 Oct 2026 11:38:26 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:48:05 PM</t>
+          <t>09 Oct 2026 01:28:36 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:51:04 AM</t>
+          <t>12 Oct 2026 11:38:26 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -6662,29 +7617,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 18h 2m</t>
+          <t>2d 22h 9m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1366549</t>
+          <t>TKT1364855</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Janak Adhikari</t>
+          <t>Sachit Achhami</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6704,22 +7659,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:10:17 PM</t>
+          <t>12 Oct 2026 11:51:04 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:28:33 PM</t>
+          <t>09 Oct 2026 05:48:05 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:10:17 PM</t>
+          <t>12 Oct 2026 11:51:04 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -6729,19 +7684,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>22h 41m</t>
+          <t>2d 18h 2m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1367312</t>
+          <t>TKT1366549</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Tilak bahadur bohora</t>
+          <t>Janak Adhikari</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -6771,22 +7726,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:04:04 PM</t>
+          <t>12 Oct 2026 12:10:17 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:28:49 AM</t>
+          <t>11 Oct 2026 01:28:33 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:04:04 PM</t>
+          <t>12 Oct 2026 12:10:17 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -6796,74 +7751,476 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>3h 35m</t>
+          <t>22h 41m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>TKT1367312</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Tilak bahadur bohora</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:28:49 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>3h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>TKT1367602</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Roji Shrestha</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 12:41:01 PM</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 10:53:33 AM</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 12:41:01 PM</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>1h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366894</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:10:46 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:52:33 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57:32 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>18h 46m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>19h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366894</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:10:46 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:52:33 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57:32 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>18h 46m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>19h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366465</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Adhikari</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:38:47 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:38:47 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:54:48 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5352,10 +5352,8 @@
           <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9848949572</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9848949572</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5445,10 +5443,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5459,7 +5455,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5555,10 +5551,8 @@
           <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9848949572</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9848949572</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5648,10 +5642,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5654,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5758,10 +5750,8 @@
           <t>Sunita Adhikari</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9840779767</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9840779767</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5851,10 +5841,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5865,7 +5853,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5961,10 +5949,8 @@
           <t>Uttam Kumar Poudel</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9824866858</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9824866858</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6050,10 +6036,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6064,7 +6048,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6160,10 +6144,8 @@
           <t>Uttam Kumar Poudel</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9824866858</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9824866858</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6249,10 +6231,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6263,32 +6243,243 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 51m</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 51m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 1:05 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>NETTV issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367427</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Ghanashyam Adhikari</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Ghanashyam Adhikari</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9851043225</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:05:03 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851043225</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:22:32 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:05:03 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.769556032831318, 85.35235214866094, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>9851043225@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>03:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6340,7 +6531,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -6350,7 +6541,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -6361,7 +6552,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6564,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 9m</t>
+          <t>6h 51m</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6576,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 56m</t>
+          <t>1d 4h 47m</t>
         </is>
       </c>
     </row>
@@ -6462,14 +6653,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6645,197 +6836,153 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-STB App not working</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1366504</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Pukal Rokka</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Damage Issue</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 12:58:44 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026 07:31:06 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1359809</t>
+          <t>TKT1366504</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Ashutosh Regmi</t>
+          <t>Pukal Rokka</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -6855,22 +7002,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 06:58:32 PM</t>
+          <t>11 Oct 2026 12:58:44 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:48:55 AM</t>
+          <t>12 Oct 2026 07:31:06 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -6880,19 +7027,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>6d 13h 50m</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1366896</t>
+          <t>TKT1359809</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Jonik Jung Thapa</t>
+          <t>Ashutosh Regmi</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6922,22 +7069,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:54:00 PM</t>
+          <t>05 Oct 2026 06:58:32 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:18:09 AM</t>
+          <t>12 Oct 2026 08:48:55 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -6947,19 +7094,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>15h 24m</t>
+          <t>6d 13h 50m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1366738</t>
+          <t>TKT1366896</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Suman Puri</t>
+          <t>Jonik Jung Thapa</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6989,22 +7136,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:04:04 PM</t>
+          <t>11 Oct 2026 05:54:00 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 09:56:03 AM</t>
+          <t>12 Oct 2026 09:18:09 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -7014,29 +7161,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>17h 51m</t>
+          <t>15h 24m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1366999</t>
+          <t>TKT1366738</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Surya moktan</t>
+          <t>Suman Puri</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7056,22 +7203,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:08:23 PM</t>
+          <t>11 Oct 2026 04:04:04 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:15:42 AM</t>
+          <t>12 Oct 2026 09:56:03 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -7081,29 +7228,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>15h 7m</t>
+          <t>17h 51m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1366755</t>
+          <t>TKT1366999</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Godhuli Enterprise</t>
+          <t>Surya moktan</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7123,22 +7270,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:25:26 AM</t>
+          <t>12 Oct 2026 10:15:42 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 04:23:45 PM</t>
+          <t>11 Oct 2026 07:08:23 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:25:26 AM</t>
+          <t>12 Oct 2026 10:15:42 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -7148,29 +7295,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>15h 7m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1366652</t>
+          <t>TKT1366755</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>karma gurung</t>
+          <t>Godhuli Enterprise</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -7190,22 +7337,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:20:22 AM</t>
+          <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:46:35 PM</t>
+          <t>11 Oct 2026 04:23:45 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:20:22 AM</t>
+          <t>12 Oct 2026 10:25:26 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -7215,29 +7362,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1366558</t>
+          <t>TKT1366652</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Rabindra Shrestha</t>
+          <t>karma gurung</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7257,22 +7404,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:59:25 AM</t>
+          <t>12 Oct 2026 10:20:22 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:34:59 PM</t>
+          <t>11 Oct 2026 02:46:35 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:59:25 AM</t>
+          <t>12 Oct 2026 10:20:22 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7282,19 +7429,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>21h 24m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1367161</t>
+          <t>TKT1366558</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Yogesh Shrestha</t>
+          <t>Rabindra Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7324,22 +7471,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:01:30 AM</t>
+          <t>12 Oct 2026 10:59:25 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:53:31 PM</t>
+          <t>11 Oct 2026 01:34:59 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:01:30 AM</t>
+          <t>12 Oct 2026 10:59:25 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7349,29 +7496,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>21h 24m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1366814</t>
+          <t>TKT1367161</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Pabitra khatri</t>
+          <t>Yogesh Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7391,22 +7538,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:09:44 AM</t>
+          <t>12 Oct 2026 11:01:30 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:12:53 PM</t>
+          <t>11 Oct 2026 08:53:31 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:09:44 AM</t>
+          <t>12 Oct 2026 11:01:30 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7416,29 +7563,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>17h 56m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1366937</t>
+          <t>TKT1366814</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Anita Bogati</t>
+          <t>Pabitra khatri</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7458,22 +7605,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:10:48 AM</t>
+          <t>12 Oct 2026 11:09:44 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 06:35:19 PM</t>
+          <t>11 Oct 2026 05:12:53 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:10:48 AM</t>
+          <t>12 Oct 2026 11:09:44 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -7483,29 +7630,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>16h 35m</t>
+          <t>17h 56m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1367285</t>
+          <t>TKT1366937</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Menuka adhikari</t>
+          <t>Anita Bogati</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -7525,22 +7672,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:28:58 AM</t>
+          <t>12 Oct 2026 11:10:48 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 07:47:07 AM</t>
+          <t>11 Oct 2026 06:35:19 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:28:58 AM</t>
+          <t>12 Oct 2026 11:10:48 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -7550,29 +7697,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>3h 41m</t>
+          <t>16h 35m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364527</t>
+          <t>TKT1367285</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Vicky Shahi</t>
+          <t>Menuka adhikari</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -7592,22 +7739,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:38:26 AM</t>
+          <t>12 Oct 2026 11:28:58 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:28:36 PM</t>
+          <t>12 Oct 2026 07:47:07 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:38:26 AM</t>
+          <t>12 Oct 2026 11:28:58 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -7617,29 +7764,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 9m</t>
+          <t>3h 41m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1364855</t>
+          <t>TKT1364527</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sachit Achhami</t>
+          <t>Vicky Shahi</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7659,22 +7806,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:51:04 AM</t>
+          <t>12 Oct 2026 11:38:26 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:48:05 PM</t>
+          <t>09 Oct 2026 01:28:36 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 11:51:04 AM</t>
+          <t>12 Oct 2026 11:38:26 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7684,29 +7831,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 18h 2m</t>
+          <t>2d 22h 9m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1366549</t>
+          <t>TKT1364855</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Janak Adhikari</t>
+          <t>Sachit Achhami</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7726,22 +7873,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:10:17 PM</t>
+          <t>12 Oct 2026 11:51:04 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:28:33 PM</t>
+          <t>09 Oct 2026 05:48:05 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:10:17 PM</t>
+          <t>12 Oct 2026 11:51:04 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -7751,19 +7898,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>22h 41m</t>
+          <t>2d 18h 2m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1367312</t>
+          <t>TKT1366549</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Tilak bahadur bohora</t>
+          <t>Janak Adhikari</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7793,22 +7940,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:04:04 PM</t>
+          <t>12 Oct 2026 12:10:17 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 08:28:49 AM</t>
+          <t>11 Oct 2026 01:28:33 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:04:04 PM</t>
+          <t>12 Oct 2026 12:10:17 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7818,19 +7965,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>3h 35m</t>
+          <t>22h 41m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1367602</t>
+          <t>TKT1367312</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Roji Shrestha</t>
+          <t>Tilak bahadur bohora</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7860,22 +8007,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:41:01 PM</t>
+          <t>12 Oct 2026 12:04:04 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 10:53:33 AM</t>
+          <t>12 Oct 2026 08:28:49 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:41:01 PM</t>
+          <t>12 Oct 2026 12:04:04 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -7885,74 +8032,74 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1h 47m</t>
+          <t>3h 35m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1366894</t>
+          <t>TKT1367602</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Shivaraj Ojhaya  Tharu</t>
+          <t>Roji Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 06:10:46 PM</t>
+          <t>12 Oct 2026 12:41:01 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 05:52:33 PM</t>
+          <t>12 Oct 2026 10:53:33 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:57:32 PM</t>
+          <t>12 Oct 2026 12:41:01 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>18h 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>19h 4m</t>
+          <t>1h 47m</t>
         </is>
       </c>
     </row>
@@ -7989,7 +8136,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -8026,22 +8173,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1366465</t>
+          <t>TKT1366894</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Sunita Adhikari</t>
+          <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8056,49 +8203,49 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:38:47 PM</t>
+          <t>11 Oct 2026 06:10:46 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:38:47 PM</t>
+          <t>11 Oct 2026 05:52:33 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:54:48 PM</t>
+          <t>12 Oct 2026 12:57:32 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1d 16m</t>
+          <t>18h 46m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 16m</t>
+          <t>19h 4m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1365507</t>
+          <t>TKT1366465</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Uttam Kumar Poudel</t>
+          <t>Sunita Adhikari</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8123,37 +8270,37 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:01:14 PM</t>
+          <t>11 Oct 2026 12:38:47 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:01:14 PM</t>
+          <t>11 Oct 2026 12:38:47 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026 12:53:02 PM</t>
+          <t>12 Oct 2026 12:54:48 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 51m</t>
+          <t>1d 16m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 51m</t>
+          <t>1d 16m</t>
         </is>
       </c>
     </row>
@@ -8190,37 +8337,171 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 01:01:14 PM</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 01:01:14 PM</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026 12:53:02 PM</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>1d 23h 51m</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>1d 23h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367427</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Ghanashyam Adhikari</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-STB App not working</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:05:03 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:22:32 AM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:05:03 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6339,10 +6339,8 @@
           <t>Ghanashyam Adhikari</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9851043225</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9851043225</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6377,10 +6375,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -6436,25 +6432,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6503,7 +6495,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8471,7 +8463,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6475,6 +6475,221 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 1:38 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367645</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Mandip Shigh</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Mandip Shigh</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9851064551</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:38:57 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9851064551</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:15:50 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:38:57 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.73937</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Digital Cube Store Details from Google Maps Ganeshthan, Kathmandu 44600 +977 980-8123241  , Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>mandipchauhan2012@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>02:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.31483</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6486,7 +6701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6495,7 +6710,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6523,7 +6738,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -6533,7 +6748,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6544,7 +6759,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6771,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 51m</t>
+          <t>6h 33m</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6783,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 47m</t>
+          <t>1d 3h 41m</t>
         </is>
       </c>
     </row>
@@ -6609,14 +6824,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -6717,14 +6932,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -8497,6 +8712,73 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367645</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Mandip Shigh</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:38:57 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:15:50 AM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:38:57 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6542,10 +6542,8 @@
           <t>Mandip Shigh</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9851064551</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9851064551</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6580,10 +6578,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.73937</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.73937</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6621,10 +6617,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH31" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH31" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
@@ -6643,25 +6637,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.31483</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.31483</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6710,7 +6700,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8745,7 +8735,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6680,6 +6680,428 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:17 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367298</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9840450592</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:07:10 AM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9840450592</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:07:10 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:17:11 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.69576</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>M7WG+JRW, Nagarjun,Near by Welcome meat mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>nischalpathak62@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>04:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.27662</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>6h 10m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>6h 10m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:15 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>replace skycom to nettv</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367473</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:40:20 AM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:40:20 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:15:22 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>04:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>4h 35m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>4h 35m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6691,16 +7113,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6728,7 +7150,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6738,7 +7160,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -6749,7 +7171,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -6761,7 +7183,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 33m</t>
+          <t>6h 28m</t>
         </is>
       </c>
     </row>
@@ -6773,7 +7195,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 41m</t>
+          <t>1d 1h 58m</t>
         </is>
       </c>
     </row>
@@ -6814,14 +7236,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -6832,14 +7254,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -6922,14 +7344,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -6968,14 +7390,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8769,6 +9191,140 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367298</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:07:10 AM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:07:10 AM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:17:11 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>6h 10m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>6h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367473</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:40:20 AM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:40:20 AM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:15:22 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>4h 35m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>4h 35m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6747,10 +6747,8 @@
           <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9840450592</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9840450592</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6785,10 +6783,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.69576</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.69576</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6844,25 +6840,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.27662</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.27661999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6958,10 +6950,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6996,10 +6986,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.699563</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.699563</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7055,25 +7043,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7122,7 +7106,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9224,7 +9208,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -9291,7 +9275,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7086,6 +7086,428 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366682</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9843174089</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9808235412</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:03:53 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.68546</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near Everest Momo Center, Kuleshor , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>anilsinghkr73@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>04:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.29819</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>23h 25m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:27 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT IN ROUTER</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367789</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9841132622</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:27:24 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>BKT9841132622</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:40:06 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:27:24 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Radheradhe, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>1@g.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>01:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L52-6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7097,16 +7519,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7134,7 +7556,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -7144,7 +7566,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -7155,7 +7577,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7589,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 28m</t>
+          <t>6h</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7601,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 58m</t>
+          <t>1d 1h 1m</t>
         </is>
       </c>
     </row>
@@ -7220,14 +7642,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -7238,14 +7660,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -7328,14 +7750,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -7420,10 +7842,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -9309,6 +9731,140 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366682</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:03:53 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>23h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367789</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Anjali Shrestha</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:27:24 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:40:06 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:27:24 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7153,10 +7153,8 @@
           <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9843174089</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9843174089</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7191,10 +7189,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.68546</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.68546</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7250,25 +7246,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.29819</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.29819000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7364,10 +7356,8 @@
           <t>Anjali Shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9841132622</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9841132622</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7402,10 +7392,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -7461,25 +7449,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L52-6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7528,7 +7512,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9764,7 +9748,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -9831,7 +9815,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW35"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7492,6 +7492,109 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 3:11 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="AA36" s="3" t="inlineStr"/>
+      <c r="AB36" s="3" t="inlineStr"/>
+      <c r="AC36" s="3" t="inlineStr"/>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7540,7 +7643,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -7561,7 +7664,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7595,6 +7595,205 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 3:11 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367703</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Gurung</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Gurung</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9843654354</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:11:20 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9843654354</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:01:36 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:11:20 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Near comedy height, baneshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>03:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>3h 9m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7606,7 +7805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7615,7 +7814,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7643,7 +7842,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -7653,7 +7852,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -7664,7 +7863,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7875,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>5h 48m</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7887,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 1m</t>
+          <t>1d 16m</t>
         </is>
       </c>
     </row>
@@ -7729,14 +7928,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -7837,14 +8036,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -9952,6 +10151,73 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367703</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Gurung</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:11:20 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:01:36 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:11:20 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>3h 9m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7662,10 +7662,8 @@
           <t>Jamuna Gurung</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9843654354</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9843654354</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7751,10 +7749,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -7765,7 +7761,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7814,7 +7810,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10184,7 +10180,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7790,6 +7790,221 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 4:10 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367847</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Pawan Ghimire</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Pawan Ghimire</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9761325251</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:10:12 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9851053640</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:22:36 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:10:12 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.70455</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>National Trauma Center new read , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>02:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB216</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.31256</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7801,7 +8016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7810,7 +8025,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7838,7 +8053,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7848,7 +8063,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -7859,7 +8074,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -7871,7 +8086,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 48m</t>
+          <t>5h 36m</t>
         </is>
       </c>
     </row>
@@ -7883,7 +8098,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16m</t>
+          <t>23h 33m</t>
         </is>
       </c>
     </row>
@@ -7924,14 +8139,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8247,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -10214,6 +10429,73 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1367847</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Pawan Ghimire</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:10:12 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:22:36 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:10:12 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7857,10 +7857,8 @@
           <t>Pawan Ghimire</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9761325251</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9761325251</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7895,10 +7893,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.70455</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.70455</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7936,10 +7932,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH38" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH38" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
@@ -7958,25 +7952,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB216</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.31256</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.31256</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -8025,7 +8015,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10462,7 +10452,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7995,6 +7995,217 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 5:26 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368012</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Akhileshwar Singh</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Akhileshwar Singh</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9841374223</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 05:26:52 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9841374223</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:31:26 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 05:26:52 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.6676</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Damodar Marga, Lalitpur,Green Tara International Overseas (P) Ltd., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>aksileshwar.singh12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>01:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.3133</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1h 55m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8006,7 +8217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8015,7 +8226,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8043,7 +8254,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -8053,7 +8264,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -8064,7 +8275,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8287,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 36m</t>
+          <t>5h 25m</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8299,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 33m</t>
+          <t>22h 51m</t>
         </is>
       </c>
     </row>
@@ -8129,14 +8340,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
@@ -8237,14 +8448,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
@@ -10486,6 +10697,73 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368012</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Akhileshwar Singh</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 05:26:52 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:31:26 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 05:26:52 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1h 55m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8062,10 +8062,8 @@
           <t>Akhileshwar Singh</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9841374223</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9841374223</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8100,10 +8098,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.6676</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.6676</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -8159,25 +8155,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.3133</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.3133</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8226,7 +8218,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10730,7 +10722,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8198,6 +8198,193 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 8:30 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>ONT Replacement</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368015</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Height Restro and wellness</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Height Restro and wellness</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9843760166</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:25 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>LS632</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:34:16 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:25 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Salesberry building Maharajgunj , , ,</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>04:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Ghising</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>4h 56m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8209,7 +8396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8218,7 +8405,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8246,7 +8433,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -8256,7 +8443,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -8267,7 +8454,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8466,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 25m</t>
+          <t>5h 15m</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8478,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 51m</t>
+          <t>22h 17m</t>
         </is>
       </c>
     </row>
@@ -8350,14 +8537,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -8532,10 +8719,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -10756,6 +10943,73 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1368015</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Height Restro and wellness</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:25 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:34:16 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:25 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>4h 56m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_12_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_12_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8255,20 +8255,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="3" t="inlineStr">
         <is>
           <t>Height Restro and wellness</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9843760166</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9843760166</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8356,7 +8350,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8405,7 +8399,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10976,7 +10970,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
